--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6231986</v>
+        <v>60918558</v>
       </c>
       <c r="B2" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224365</v>
+        <v>2082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbäcken Järvsand, Jmt</t>
+          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537885.0335179419</v>
+        <v>537908</v>
       </c>
       <c r="R2" t="n">
-        <v>7096131.99341028</v>
+        <v>7096080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets. Vid stig i gammal täkt.</t>
+          <t>Gransumpskog med ca 30 % björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +762,10 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vid stig i gammal täkt</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -797,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6194896</v>
+        <v>60185559</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,30 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224358</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storbäcken Järvsand, Jmt</t>
+          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537885.0335179419</v>
+        <v>537885</v>
       </c>
       <c r="R3" t="n">
-        <v>7096131.99341028</v>
+        <v>7096132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,27 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets, ca 4,5 km nordväst om Lövberga Vid stig i gammal täkt.</t>
+          <t>Vid stig i gammal täkt,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,15 +864,10 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vid stig i gammal täkt</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -915,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60918558</v>
+        <v>6231986</v>
       </c>
       <c r="B4" t="n">
-        <v>97552</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2082</v>
+        <v>224365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Riplummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Grev. &amp; Hook.) Selander</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
+          <t>Storbäcken Järvsand, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537907.6495420589</v>
+        <v>537885</v>
       </c>
       <c r="R4" t="n">
-        <v>7096079.586129761</v>
+        <v>7096132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,27 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-08-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gransumpskog med ca 30 % björk.</t>
+          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets. Vid stig i gammal täkt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +966,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vid stig i gammal täkt</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60918558</v>
+        <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>100387</v>
+        <v>101376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2082</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
+          <t>Järilån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537908</v>
+        <v>537830</v>
       </c>
       <c r="R2" t="n">
-        <v>7096080</v>
+        <v>7096108</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gransumpskog med ca 30 % björk.</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,28 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60185559</v>
+        <v>60918558</v>
       </c>
       <c r="B3" t="n">
-        <v>97989</v>
+        <v>100387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537885</v>
+        <v>537908</v>
       </c>
       <c r="R3" t="n">
-        <v>7096132</v>
+        <v>7096080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid stig i gammal täkt,</t>
+          <t>Gransumpskog med ca 30 % björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6231986</v>
+        <v>60185559</v>
       </c>
       <c r="B4" t="n">
-        <v>97988</v>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,27 +890,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224365</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbäcken Järvsand, Jmt</t>
+          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets. Vid stig i gammal täkt.</t>
+          <t>Vid stig i gammal täkt,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,24 +965,126 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vid stig i gammal täkt</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6231986</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97988</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224365</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Riplummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storbäcken Järvsand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537885</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7096132</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2000-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2000-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets. Vid stig i gammal täkt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vid stig i gammal täkt</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Bengt Petterson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134356590</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60918558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60185559</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,8 +1105,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6231986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60918558</v>
+        <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>100387</v>
+        <v>101456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2082</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
+          <t>Järilån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537908</v>
+        <v>537830</v>
       </c>
       <c r="R2" t="n">
-        <v>7096080</v>
+        <v>7096108</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gransumpskog med ca 30 % björk.</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,33 +763,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60918558</t>
+          <t>https://artportalen.se/Sighting/134356590</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60185559</v>
+        <v>60918558</v>
       </c>
       <c r="B3" t="n">
-        <v>97989</v>
+        <v>100387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537885</v>
+        <v>537908</v>
       </c>
       <c r="R3" t="n">
-        <v>7096132</v>
+        <v>7096080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid stig i gammal täkt,</t>
+          <t>Gransumpskog med ca 30 % björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,16 +888,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60185559</t>
+          <t>https://artportalen.se/Sighting/60918558</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6231986</v>
+        <v>60185559</v>
       </c>
       <c r="B4" t="n">
-        <v>97988</v>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,27 +905,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224365</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbäcken Järvsand, Jmt</t>
+          <t>Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca , Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -959,17 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets. Vid stig i gammal täkt.</t>
+          <t>Vid stig i gammal täkt,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +981,10 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vid stig i gammal täkt</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -999,6 +994,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60185559</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6231986</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97988</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224365</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Riplummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storbäcken Järvsand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537885</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7096132</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2000-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2000-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Observatör Bengt Petterson. Storbäcken, Järvsand 1:22, mellan vägen tilll Järilvattnet och Järilån, ca 500 m norr om Fettjorna, ca 1,9 km ostnordost om Kattögeltjärnens nordspets. Vid stig i gammal täkt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vid stig i gammal täkt</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6231986</t>
         </is>
@@ -1009,6 +1116,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32794-2025 artfynd.xlsx
+++ b/artfynd/A 32794-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134356590</v>
       </c>
       <c r="B2" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
